--- a/report_forms/019_supply_chain_efficiency_summary_report--report_forms.xlsx
+++ b/report_forms/019_supply_chain_efficiency_summary_report--report_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -884,8 +884,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -913,12 +913,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'metric_1',_'label':_'metric_1'}</t>
+          <t>metric_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'metric_1', 'label': 'Metric 1'}</t>
+          <t>Metric 1</t>
         </is>
       </c>
     </row>
@@ -930,12 +930,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'metric_2',_'label':_'metric_2'}</t>
+          <t>metric_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'metric_2', 'label': 'Metric 2'}</t>
+          <t>Metric 2</t>
         </is>
       </c>
     </row>
@@ -947,12 +947,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'metric_3',_'label':_'metric_3'}</t>
+          <t>metric_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'metric_3', 'label': 'Metric 3'}</t>
+          <t>Metric 3</t>
         </is>
       </c>
     </row>
@@ -964,12 +964,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'metric_4',_'label':_'metric_4'}</t>
+          <t>metric_4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'metric_4', 'label': 'Metric 4'}</t>
+          <t>Metric 4</t>
         </is>
       </c>
     </row>
@@ -981,12 +981,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'metric_5',_'label':_'metric_5'}</t>
+          <t>metric_5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'metric_5', 'label': 'Metric 5'}</t>
+          <t>Metric 5</t>
         </is>
       </c>
     </row>
@@ -998,12 +998,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_'metric_6',_'label':_'metric_6'}</t>
+          <t>metric_6</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 'metric_6', 'label': 'Metric 6'}</t>
+          <t>Metric 6</t>
         </is>
       </c>
     </row>
@@ -1015,12 +1015,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'submit_now',_'label':_'submit_now'}</t>
+          <t>submit_now</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'submit_now', 'label': 'Submit Now'}</t>
+          <t>Submit Now</t>
         </is>
       </c>
     </row>
@@ -1032,12 +1032,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'save_for_later',_'label':_'save_for_later'}</t>
+          <t>save_for_later</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'save_for_later', 'label': 'Save for Later'}</t>
+          <t>Save for Later</t>
         </is>
       </c>
     </row>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'attachment_1',_'label':_'attachment_1'}</t>
+          <t>attachment_1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'attachment_1', 'label': 'Attachment 1'}</t>
+          <t>Attachment 1</t>
         </is>
       </c>
     </row>
@@ -1066,12 +1066,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'attachment_2',_'label':_'attachment_2'}</t>
+          <t>attachment_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'attachment_2', 'label': 'Attachment 2'}</t>
+          <t>Attachment 2</t>
         </is>
       </c>
     </row>
@@ -1083,12 +1083,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'attachment_3',_'label':_'attachment_3'}</t>
+          <t>attachment_3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'attachment_3', 'label': 'Attachment 3'}</t>
+          <t>Attachment 3</t>
         </is>
       </c>
     </row>
@@ -1100,12 +1100,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'attachment_4',_'label':_'attachment_4'}</t>
+          <t>attachment_4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'attachment_4', 'label': 'Attachment 4'}</t>
+          <t>Attachment 4</t>
         </is>
       </c>
     </row>
@@ -1117,12 +1117,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'user_1',_'label':_'user_1'}</t>
+          <t>user_1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'user_1', 'label': 'User 1'}</t>
+          <t>User 1</t>
         </is>
       </c>
     </row>
@@ -1134,12 +1134,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'user_2',_'label':_'user_2'}</t>
+          <t>user_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'user_2', 'label': 'User 2'}</t>
+          <t>User 2</t>
         </is>
       </c>
     </row>
